--- a/[과제] 폐교 맵 포트폴리오.xlsx
+++ b/[과제] 폐교 맵 포트폴리오.xlsx
@@ -33,20 +33,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -84,6 +77,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFBD28F8"/>
+      <color rgb="FFF43F2C"/>
+      <color rgb="FF50BFF6"/>
+      <color rgb="FF87DA70"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -451,6 +452,1355 @@
           <a:r>
             <a:rPr lang="ko-KR" altLang="en-US" sz="2000"/>
             <a:t>학교 폭력의 흔적과 </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>523874</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>661989</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>497331</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>333374</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FDFDFD"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FDFDFD">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="19649" t="16320" r="19775" b="18823"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28146374" y="26903364"/>
+          <a:ext cx="5497957" cy="5886448"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>214311</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="모서리가 둥근 직사각형 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1381126" y="37528499"/>
+          <a:ext cx="4833936" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="92D050"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스의 트라우마가 가장 큰 장소인 강당</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 페이즈 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 보스 외형 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로 시작한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>배구공</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>뜀틀인 상호작용 구조물을 활용하여 보스와 전투한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>33338</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>33338</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>-1</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>23814</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="모서리가 둥근 직사각형 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1414463" y="36633151"/>
+          <a:ext cx="4800599" cy="681038"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="87DA70"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>발단</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>223837</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>24077</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>200024</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="모서리가 둥근 직사각형 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6891338" y="37514212"/>
+          <a:ext cx="4872302" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="50BFF6"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스의 트라우마가 가장 큰 장소인 강당</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 페이즈 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 보스 외형 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로 시작한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>배구공</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>뜀틀인 상호작용 구조물을 활용하여 보스와 전투한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>23812</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>9527</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="모서리가 둥근 직사각형 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6924675" y="36618864"/>
+          <a:ext cx="4838700" cy="681038"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="50BFF6"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>전개</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>204785</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>23811</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>180972</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="모서리가 둥근 직사각형 10"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12453938" y="37495160"/>
+          <a:ext cx="4833936" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent4">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스의 트라우마가 가장 큰 장소인 강당</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 페이즈 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 보스 외형 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로 시작한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>배구공</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>뜀틀인 상호작용 구조물을 활용하여 보스와 전투한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>-1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>23811</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>681037</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="모서리가 둥근 직사각형 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12430125" y="36599812"/>
+          <a:ext cx="4857749" cy="681038"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>위기</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>228599</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>690561</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>204786</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="모서리가 둥근 직사각형 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17954625" y="37518974"/>
+          <a:ext cx="4833936" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="F43F2C"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스의 트라우마가 가장 큰 장소인 강당</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 페이즈 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 보스 외형 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로 시작한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>배구공</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>뜀틀인 상호작용 구조물을 활용하여 보스와 전투한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>23813</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>690561</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>14289</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="모서리가 둥근 직사각형 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17987962" y="36623626"/>
+          <a:ext cx="4800599" cy="681038"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="F43F2C"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>절정</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>228598</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>690561</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>204785</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="모서리가 둥근 직사각형 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23479125" y="37518973"/>
+          <a:ext cx="4833936" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:solidFill>
+            <a:srgbClr val="BD28F8"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스의 트라우마가 가장 큰 장소인 강당</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보스</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 페이즈 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 보스 외형 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>로 시작한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" altLang="ko-KR" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>배구공</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>뜀틀인 상호작용 구조물을 활용하여 보스와 전투한다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="2000">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>23812</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>690561</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>14288</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="모서리가 둥근 직사각형 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23512462" y="36623625"/>
+          <a:ext cx="4800599" cy="681038"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10606"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="BD28F8"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="3000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>결말</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -728,7 +2078,7 @@
   <sheetData>
     <row r="5" spans="10:10" ht="54" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/[과제] 폐교 맵 포트폴리오.xlsx
+++ b/[과제] 폐교 맵 포트폴리오.xlsx
@@ -460,16 +460,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>40</xdr:col>
-      <xdr:colOff>523874</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>661989</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>21647</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>571500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>497331</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>333374</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>637163</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>25723</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -501,8 +501,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28146374" y="26903364"/>
-          <a:ext cx="5497957" cy="5886448"/>
+          <a:off x="714374" y="20660591"/>
+          <a:ext cx="13084607" cy="14001496"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1805,6 +1805,112 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>285749</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>114</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>219449</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="그림 16"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FFFFFF"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FFFFFF">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="28186" b="28186"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="51625499" y="0"/>
+          <a:ext cx="24955501" cy="10887449"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>150000</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>71</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>429051</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="그림 17"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:clrChange>
+            <a:clrFrom>
+              <a:srgbClr val="FEFEFE"/>
+            </a:clrFrom>
+            <a:clrTo>
+              <a:srgbClr val="FEFEFE">
+                <a:alpha val="0"/>
+              </a:srgbClr>
+            </a:clrTo>
+          </a:clrChange>
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="30750" b="20385"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24819750" y="0"/>
+          <a:ext cx="22710000" cy="11097051"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
